--- a/data/BerkDataRAW.xlsx
+++ b/data/BerkDataRAW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBA99F4-60D9-4A43-90BE-0B4E27A1FA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4AA261-87C8-4D0F-A23A-299AB3FFA921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="24460" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -1612,9 +1612,27 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13E2C1E5-750D-41DB-9B65-6BB2693C1164}" name="Table1" displayName="Table1" ref="A1:T510" totalsRowShown="0">
-  <autoFilter ref="A1:T510" xr:uid="{13E2C1E5-750D-41DB-9B65-6BB2693C1164}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T510">
-    <sortCondition ref="C1:C510"/>
+  <autoFilter ref="A1:T510" xr:uid="{13E2C1E5-750D-41DB-9B65-6BB2693C1164}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="ATA 102"/>
+        <filter val="HOBİ 108"/>
+        <filter val="HOBİ 118"/>
+        <filter val="HOBİ 122"/>
+        <filter val="PFE 202"/>
+        <filter val="PFE 204"/>
+        <filter val="PFE 302"/>
+        <filter val="PFE 304"/>
+        <filter val="TDB 102"/>
+        <filter val="TDP 100"/>
+        <filter val="TDP 304"/>
+        <filter val="YBD 102"/>
+        <filter val="YBD 104"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:T510">
+    <sortCondition ref="E1:E510"/>
   </sortState>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{604663FC-0ACC-4DD6-88B4-5F8C850714F8}" name="FacultyName"/>
@@ -1913,7 +1931,7 @@
     <col min="3" max="3" width="17.08984375" customWidth="1"/>
     <col min="4" max="4" width="33.7265625" customWidth="1"/>
     <col min="5" max="5" width="12.81640625" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="6" max="6" width="27.453125" customWidth="1"/>
     <col min="7" max="7" width="10.08984375" customWidth="1"/>
     <col min="8" max="8" width="14.90625" customWidth="1"/>
     <col min="9" max="9" width="18.90625" customWidth="1"/>
@@ -1989,7 +2007,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2113,7 +2131,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -2175,7 +2193,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2237,7 +2255,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2299,7 +2317,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2361,7 +2379,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2423,7 +2441,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2485,7 +2503,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2547,7 +2565,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2609,7 +2627,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2671,7 +2689,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -2733,7 +2751,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2795,7 +2813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -2857,7 +2875,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -2927,43 +2945,43 @@
         <v>8</v>
       </c>
       <c r="C17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>204</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="G17">
-        <v>6291544</v>
+        <v>6287246</v>
       </c>
       <c r="H17" t="s">
         <v>23</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
       <c r="K17">
-        <v>6291544</v>
+        <v>6287246</v>
       </c>
       <c r="L17" t="s">
         <v>24</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17">
         <v>2</v>
@@ -2972,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S17">
-        <v>1295362</v>
+        <v>2371960</v>
       </c>
       <c r="T17">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.35">
@@ -2989,19 +3007,19 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>204</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="G18">
-        <v>6291548</v>
+        <v>6269610</v>
       </c>
       <c r="H18" t="s">
         <v>23</v>
@@ -3013,19 +3031,19 @@
         <v>2</v>
       </c>
       <c r="K18">
-        <v>6291548</v>
+        <v>6269610</v>
       </c>
       <c r="L18" t="s">
         <v>24</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18">
         <v>2</v>
@@ -3034,16 +3052,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S18">
-        <v>1295362</v>
+        <v>7133804</v>
       </c>
       <c r="T18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -3105,7 +3123,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3175,19 +3193,19 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>275</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>276</v>
+        <v>54</v>
       </c>
       <c r="G21">
-        <v>6274499</v>
+        <v>6285584</v>
       </c>
       <c r="H21" t="s">
         <v>23</v>
@@ -3196,10 +3214,10 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21">
-        <v>6274499</v>
+        <v>6285584</v>
       </c>
       <c r="L21" t="s">
         <v>24</v>
@@ -3211,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21">
         <v>2</v>
@@ -3223,13 +3241,13 @@
         <v>25</v>
       </c>
       <c r="S21">
-        <v>4339346</v>
+        <v>1145553</v>
       </c>
       <c r="T21">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -3291,7 +3309,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -3353,7 +3371,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -3415,7 +3433,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -3477,7 +3495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -3539,7 +3557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -3601,7 +3619,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -3663,7 +3681,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -3725,7 +3743,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -3787,7 +3805,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -3849,7 +3867,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -3919,19 +3937,19 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>369</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
-        <v>370</v>
+        <v>54</v>
       </c>
       <c r="G33">
-        <v>6275905</v>
+        <v>6279383</v>
       </c>
       <c r="H33" t="s">
         <v>23</v>
@@ -3940,37 +3958,37 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>6275905</v>
+        <v>6279383</v>
       </c>
       <c r="L33" t="s">
         <v>24</v>
       </c>
       <c r="M33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33">
         <v>0</v>
       </c>
       <c r="O33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q33">
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S33">
-        <v>5791023</v>
+        <v>2826511</v>
       </c>
       <c r="T33">
-        <v>1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.35">
@@ -3981,58 +3999,58 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E34" t="s">
-        <v>369</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
-        <v>370</v>
+        <v>54</v>
       </c>
       <c r="G34">
-        <v>6275908</v>
+        <v>6285519</v>
       </c>
       <c r="H34" t="s">
         <v>23</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K34">
-        <v>6275908</v>
+        <v>6285519</v>
       </c>
       <c r="L34" t="s">
         <v>24</v>
       </c>
       <c r="M34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34">
         <v>0</v>
       </c>
       <c r="O34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q34">
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S34">
-        <v>1683449</v>
+        <v>2047115</v>
       </c>
       <c r="T34">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.35">
@@ -4043,58 +4061,58 @@
         <v>8</v>
       </c>
       <c r="C35">
-        <v>35</v>
+        <v>808</v>
       </c>
       <c r="D35" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>369</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
-        <v>370</v>
+        <v>54</v>
       </c>
       <c r="G35">
-        <v>6275909</v>
+        <v>6279433</v>
       </c>
       <c r="H35" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K35">
-        <v>6275909</v>
+        <v>6279433</v>
       </c>
       <c r="L35" t="s">
         <v>24</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35">
         <v>0</v>
       </c>
       <c r="O35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q35">
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S35">
-        <v>1542401</v>
+        <v>4256585</v>
       </c>
       <c r="T35">
-        <v>4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.35">
@@ -4105,19 +4123,19 @@
         <v>8</v>
       </c>
       <c r="C36">
-        <v>35</v>
+        <v>1040</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>371</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>372</v>
+        <v>54</v>
       </c>
       <c r="G36">
-        <v>6275906</v>
+        <v>6287246</v>
       </c>
       <c r="H36" t="s">
         <v>23</v>
@@ -4126,10 +4144,10 @@
         <v>1</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>6275906</v>
+        <v>6287246</v>
       </c>
       <c r="L36" t="s">
         <v>24</v>
@@ -4150,13 +4168,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S36">
-        <v>2662315</v>
+        <v>2371960</v>
       </c>
       <c r="T36">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.35">
@@ -4167,31 +4185,31 @@
         <v>8</v>
       </c>
       <c r="C37">
-        <v>35</v>
+        <v>1040</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>371</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>372</v>
+        <v>54</v>
       </c>
       <c r="G37">
-        <v>6275910</v>
+        <v>6290180</v>
       </c>
       <c r="H37" t="s">
         <v>23</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>6275910</v>
+        <v>6290180</v>
       </c>
       <c r="L37" t="s">
         <v>24</v>
@@ -4203,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="O37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P37">
         <v>2</v>
@@ -4212,13 +4230,13 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S37">
-        <v>2475800</v>
+        <v>2371960</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.35">
@@ -4229,31 +4247,31 @@
         <v>8</v>
       </c>
       <c r="C38">
-        <v>35</v>
+        <v>10355</v>
       </c>
       <c r="D38" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E38" t="s">
-        <v>371</v>
+        <v>53</v>
       </c>
       <c r="F38" t="s">
-        <v>372</v>
+        <v>54</v>
       </c>
       <c r="G38">
-        <v>6275911</v>
+        <v>6279383</v>
       </c>
       <c r="H38" t="s">
         <v>23</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38">
-        <v>6275911</v>
+        <v>6279383</v>
       </c>
       <c r="L38" t="s">
         <v>24</v>
@@ -4265,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="O38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38">
         <v>2</v>
@@ -4274,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S38">
-        <v>1138064</v>
+        <v>2826511</v>
       </c>
       <c r="T38">
         <v>2</v>
@@ -4297,37 +4315,37 @@
         <v>32</v>
       </c>
       <c r="E39" t="s">
-        <v>425</v>
+        <v>204</v>
       </c>
       <c r="F39" t="s">
-        <v>426</v>
+        <v>205</v>
       </c>
       <c r="G39">
-        <v>6275907</v>
+        <v>6291544</v>
       </c>
       <c r="H39" t="s">
         <v>23</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39">
-        <v>6275907</v>
+        <v>6291544</v>
       </c>
       <c r="L39" t="s">
         <v>24</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N39">
         <v>0</v>
       </c>
       <c r="O39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P39">
         <v>2</v>
@@ -4339,7 +4357,7 @@
         <v>28</v>
       </c>
       <c r="S39">
-        <v>3003404</v>
+        <v>1295362</v>
       </c>
       <c r="T39">
         <v>1</v>
@@ -4359,37 +4377,37 @@
         <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>425</v>
+        <v>204</v>
       </c>
       <c r="F40" t="s">
-        <v>426</v>
+        <v>205</v>
       </c>
       <c r="G40">
-        <v>6275913</v>
+        <v>6291548</v>
       </c>
       <c r="H40" t="s">
         <v>23</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40">
-        <v>6275913</v>
+        <v>6291548</v>
       </c>
       <c r="L40" t="s">
         <v>24</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N40">
         <v>0</v>
       </c>
       <c r="O40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P40">
         <v>2</v>
@@ -4401,10 +4419,10 @@
         <v>28</v>
       </c>
       <c r="S40">
-        <v>2471821</v>
+        <v>1295362</v>
       </c>
       <c r="T40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.35">
@@ -4415,43 +4433,43 @@
         <v>8</v>
       </c>
       <c r="C41">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E41" t="s">
-        <v>425</v>
+        <v>204</v>
       </c>
       <c r="F41" t="s">
-        <v>426</v>
+        <v>205</v>
       </c>
       <c r="G41">
-        <v>6275915</v>
+        <v>6291544</v>
       </c>
       <c r="H41" t="s">
         <v>23</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41">
-        <v>6275915</v>
+        <v>6291544</v>
       </c>
       <c r="L41" t="s">
         <v>24</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N41">
         <v>0</v>
       </c>
       <c r="O41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P41">
         <v>2</v>
@@ -4463,13 +4481,13 @@
         <v>28</v>
       </c>
       <c r="S41">
-        <v>3002026</v>
+        <v>1295362</v>
       </c>
       <c r="T41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -4531,7 +4549,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -4593,7 +4611,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -4655,7 +4673,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -4717,7 +4735,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -4787,31 +4805,31 @@
         <v>8</v>
       </c>
       <c r="C47">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E47" t="s">
-        <v>464</v>
+        <v>204</v>
       </c>
       <c r="F47" t="s">
-        <v>465</v>
+        <v>205</v>
       </c>
       <c r="G47">
-        <v>6291558</v>
+        <v>6291546</v>
       </c>
       <c r="H47" t="s">
         <v>23</v>
       </c>
       <c r="I47">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47">
-        <v>6291558</v>
+        <v>6291546</v>
       </c>
       <c r="L47" t="s">
         <v>24</v>
@@ -4835,13 +4853,13 @@
         <v>28</v>
       </c>
       <c r="S47">
-        <v>1833141</v>
+        <v>1295362</v>
       </c>
       <c r="T47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -4903,7 +4921,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>19</v>
       </c>
@@ -4973,37 +4991,37 @@
         <v>8</v>
       </c>
       <c r="C50">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>479</v>
+        <v>204</v>
       </c>
       <c r="F50" t="s">
-        <v>480</v>
+        <v>205</v>
       </c>
       <c r="G50">
-        <v>6282337</v>
+        <v>6291544</v>
       </c>
       <c r="H50" t="s">
         <v>23</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50">
         <v>2</v>
       </c>
       <c r="K50">
-        <v>6282337</v>
+        <v>6291544</v>
       </c>
       <c r="L50" t="s">
         <v>24</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N50">
         <v>0</v>
@@ -5018,16 +5036,16 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S50">
-        <v>2782610</v>
+        <v>1295362</v>
       </c>
       <c r="T50">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -5089,7 +5107,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -5151,7 +5169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>19</v>
       </c>
@@ -5213,7 +5231,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>19</v>
       </c>
@@ -5275,7 +5293,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -5337,7 +5355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -5399,7 +5417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -5461,7 +5479,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -5523,7 +5541,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -5593,43 +5611,43 @@
         <v>8</v>
       </c>
       <c r="C60">
-        <v>36</v>
+        <v>1040</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>204</v>
       </c>
       <c r="F60" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="G60">
-        <v>6287246</v>
+        <v>6291545</v>
       </c>
       <c r="H60" t="s">
         <v>23</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J60">
         <v>2</v>
       </c>
       <c r="K60">
-        <v>6287246</v>
+        <v>6291545</v>
       </c>
       <c r="L60" t="s">
         <v>24</v>
       </c>
       <c r="M60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N60">
         <v>0</v>
       </c>
       <c r="O60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P60">
         <v>2</v>
@@ -5638,16 +5656,16 @@
         <v>0</v>
       </c>
       <c r="R60" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S60">
-        <v>2371960</v>
+        <v>1295362</v>
       </c>
       <c r="T60">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>19</v>
       </c>
@@ -5709,7 +5727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>19</v>
       </c>
@@ -5771,7 +5789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>19</v>
       </c>
@@ -5833,7 +5851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>19</v>
       </c>
@@ -5895,7 +5913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -5957,7 +5975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -6019,7 +6037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -6081,7 +6099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>19</v>
       </c>
@@ -6143,7 +6161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -6205,7 +6223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -6267,7 +6285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>19</v>
       </c>
@@ -6329,7 +6347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>19</v>
       </c>
@@ -6391,7 +6409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -6453,7 +6471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>19</v>
       </c>
@@ -6515,7 +6533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>19</v>
       </c>
@@ -6577,7 +6595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -6639,7 +6657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>19</v>
       </c>
@@ -6701,7 +6719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -6763,7 +6781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>19</v>
       </c>
@@ -6825,7 +6843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>19</v>
       </c>
@@ -6887,7 +6905,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>19</v>
       </c>
@@ -6949,7 +6967,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>19</v>
       </c>
@@ -7011,7 +7029,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>19</v>
       </c>
@@ -7073,7 +7091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>19</v>
       </c>
@@ -7135,7 +7153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>19</v>
       </c>
@@ -7197,7 +7215,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>19</v>
       </c>
@@ -7259,7 +7277,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>19</v>
       </c>
@@ -7321,7 +7339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>19</v>
       </c>
@@ -7383,7 +7401,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>19</v>
       </c>
@@ -7445,7 +7463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>19</v>
       </c>
@@ -7507,7 +7525,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>19</v>
       </c>
@@ -7569,7 +7587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>19</v>
       </c>
@@ -7631,7 +7649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>19</v>
       </c>
@@ -7693,7 +7711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -7755,7 +7773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>19</v>
       </c>
@@ -7817,7 +7835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -7887,19 +7905,19 @@
         <v>8</v>
       </c>
       <c r="C97">
-        <v>36</v>
+        <v>1040</v>
       </c>
       <c r="D97" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E97" t="s">
-        <v>471</v>
+        <v>204</v>
       </c>
       <c r="F97" t="s">
-        <v>472</v>
+        <v>205</v>
       </c>
       <c r="G97">
-        <v>6278240</v>
+        <v>6291548</v>
       </c>
       <c r="H97" t="s">
         <v>23</v>
@@ -7908,22 +7926,22 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K97">
-        <v>6278240</v>
+        <v>6291548</v>
       </c>
       <c r="L97" t="s">
         <v>24</v>
       </c>
       <c r="M97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N97">
         <v>0</v>
       </c>
       <c r="O97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P97">
         <v>2</v>
@@ -7935,10 +7953,10 @@
         <v>28</v>
       </c>
       <c r="S97">
-        <v>2355205</v>
+        <v>1295362</v>
       </c>
       <c r="T97">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.35">
@@ -7949,37 +7967,37 @@
         <v>8</v>
       </c>
       <c r="C98">
-        <v>36</v>
+        <v>1040</v>
       </c>
       <c r="D98" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E98" t="s">
-        <v>479</v>
+        <v>204</v>
       </c>
       <c r="F98" t="s">
-        <v>480</v>
+        <v>205</v>
       </c>
       <c r="G98">
-        <v>6282338</v>
+        <v>6291549</v>
       </c>
       <c r="H98" t="s">
         <v>23</v>
       </c>
       <c r="I98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J98">
         <v>2</v>
       </c>
       <c r="K98">
-        <v>6282338</v>
+        <v>6291549</v>
       </c>
       <c r="L98" t="s">
         <v>24</v>
       </c>
       <c r="M98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N98">
         <v>0</v>
@@ -7994,16 +8012,16 @@
         <v>0</v>
       </c>
       <c r="R98" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S98">
-        <v>2692386</v>
+        <v>1295362</v>
       </c>
       <c r="T98">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>19</v>
       </c>
@@ -8079,13 +8097,13 @@
         <v>41</v>
       </c>
       <c r="E100" t="s">
-        <v>42</v>
+        <v>321</v>
       </c>
       <c r="F100" t="s">
-        <v>43</v>
+        <v>322</v>
       </c>
       <c r="G100">
-        <v>6269609</v>
+        <v>6291541</v>
       </c>
       <c r="H100" t="s">
         <v>23</v>
@@ -8094,16 +8112,16 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K100">
-        <v>6269609</v>
+        <v>6291541</v>
       </c>
       <c r="L100" t="s">
         <v>24</v>
       </c>
       <c r="M100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N100">
         <v>0</v>
@@ -8121,13 +8139,13 @@
         <v>28</v>
       </c>
       <c r="S100">
-        <v>5746361</v>
+        <v>4417332</v>
       </c>
       <c r="T100">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -8197,43 +8215,43 @@
         <v>8</v>
       </c>
       <c r="C102">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D102" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E102" t="s">
-        <v>53</v>
+        <v>464</v>
       </c>
       <c r="F102" t="s">
-        <v>54</v>
+        <v>465</v>
       </c>
       <c r="G102">
-        <v>6269610</v>
+        <v>6291558</v>
       </c>
       <c r="H102" t="s">
         <v>23</v>
       </c>
       <c r="I102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J102">
         <v>2</v>
       </c>
       <c r="K102">
-        <v>6269610</v>
+        <v>6291558</v>
       </c>
       <c r="L102" t="s">
         <v>24</v>
       </c>
       <c r="M102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N102">
         <v>0</v>
       </c>
       <c r="O102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P102">
         <v>2</v>
@@ -8242,16 +8260,16 @@
         <v>0</v>
       </c>
       <c r="R102" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S102">
-        <v>7133804</v>
+        <v>1833141</v>
       </c>
       <c r="T102">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -8313,7 +8331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -8375,7 +8393,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -8437,7 +8455,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>19</v>
       </c>
@@ -8499,7 +8517,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>19</v>
       </c>
@@ -8561,7 +8579,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>19</v>
       </c>
@@ -8623,7 +8641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>19</v>
       </c>
@@ -8685,7 +8703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>19</v>
       </c>
@@ -8747,7 +8765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>19</v>
       </c>
@@ -8809,7 +8827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>19</v>
       </c>
@@ -8871,7 +8889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>19</v>
       </c>
@@ -8933,7 +8951,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>19</v>
       </c>
@@ -8995,7 +9013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>19</v>
       </c>
@@ -9057,7 +9075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>19</v>
       </c>
@@ -9119,7 +9137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>19</v>
       </c>
@@ -9181,7 +9199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>19</v>
       </c>
@@ -9243,7 +9261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>19</v>
       </c>
@@ -9305,7 +9323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>19</v>
       </c>
@@ -9367,7 +9385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>19</v>
       </c>
@@ -9429,7 +9447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>19</v>
       </c>
@@ -9491,7 +9509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>19</v>
       </c>
@@ -9553,7 +9571,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>19</v>
       </c>
@@ -9615,7 +9633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>19</v>
       </c>
@@ -9677,7 +9695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>19</v>
       </c>
@@ -9739,7 +9757,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>19</v>
       </c>
@@ -9801,7 +9819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>19</v>
       </c>
@@ -9863,7 +9881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>19</v>
       </c>
@@ -9925,7 +9943,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>19</v>
       </c>
@@ -10001,13 +10019,13 @@
         <v>41</v>
       </c>
       <c r="E131" t="s">
-        <v>204</v>
+        <v>464</v>
       </c>
       <c r="F131" t="s">
-        <v>205</v>
+        <v>465</v>
       </c>
       <c r="G131">
-        <v>6291544</v>
+        <v>6291558</v>
       </c>
       <c r="H131" t="s">
         <v>23</v>
@@ -10019,7 +10037,7 @@
         <v>2</v>
       </c>
       <c r="K131">
-        <v>6291544</v>
+        <v>6291558</v>
       </c>
       <c r="L131" t="s">
         <v>24</v>
@@ -10043,7 +10061,7 @@
         <v>28</v>
       </c>
       <c r="S131">
-        <v>1295362</v>
+        <v>1833141</v>
       </c>
       <c r="T131">
         <v>1</v>
@@ -10057,31 +10075,31 @@
         <v>8</v>
       </c>
       <c r="C132">
-        <v>37</v>
+        <v>1040</v>
       </c>
       <c r="D132" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E132" t="s">
-        <v>204</v>
+        <v>464</v>
       </c>
       <c r="F132" t="s">
-        <v>205</v>
+        <v>465</v>
       </c>
       <c r="G132">
-        <v>6291546</v>
+        <v>6291552</v>
       </c>
       <c r="H132" t="s">
         <v>23</v>
       </c>
       <c r="I132">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J132">
         <v>2</v>
       </c>
       <c r="K132">
-        <v>6291546</v>
+        <v>6291552</v>
       </c>
       <c r="L132" t="s">
         <v>24</v>
@@ -10105,13 +10123,13 @@
         <v>28</v>
       </c>
       <c r="S132">
-        <v>1295362</v>
+        <v>1833141</v>
       </c>
       <c r="T132">
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>19</v>
       </c>
@@ -10173,7 +10191,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -10235,7 +10253,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>19</v>
       </c>
@@ -10297,7 +10315,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>19</v>
       </c>
@@ -10359,7 +10377,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>19</v>
       </c>
@@ -10421,7 +10439,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>19</v>
       </c>
@@ -10491,19 +10509,19 @@
         <v>8</v>
       </c>
       <c r="C139">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D139" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E139" t="s">
-        <v>275</v>
+        <v>369</v>
       </c>
       <c r="F139" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="G139">
-        <v>6274499</v>
+        <v>6275905</v>
       </c>
       <c r="H139" t="s">
         <v>23</v>
@@ -10515,37 +10533,37 @@
         <v>4</v>
       </c>
       <c r="K139">
-        <v>6274499</v>
+        <v>6275905</v>
       </c>
       <c r="L139" t="s">
         <v>24</v>
       </c>
       <c r="M139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N139">
         <v>0</v>
       </c>
       <c r="O139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q139">
         <v>0</v>
       </c>
       <c r="R139" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S139">
-        <v>4339346</v>
+        <v>5791023</v>
       </c>
       <c r="T139">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>19</v>
       </c>
@@ -10607,7 +10625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -10669,7 +10687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>19</v>
       </c>
@@ -10731,7 +10749,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>19</v>
       </c>
@@ -10793,7 +10811,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>19</v>
       </c>
@@ -10855,7 +10873,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>19</v>
       </c>
@@ -10925,46 +10943,46 @@
         <v>8</v>
       </c>
       <c r="C146">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D146" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E146" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="F146" t="s">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="G146">
-        <v>6291541</v>
+        <v>6275908</v>
       </c>
       <c r="H146" t="s">
         <v>23</v>
       </c>
       <c r="I146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J146">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K146">
-        <v>6291541</v>
+        <v>6275908</v>
       </c>
       <c r="L146" t="s">
         <v>24</v>
       </c>
       <c r="M146">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N146">
         <v>0</v>
       </c>
       <c r="O146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -10973,13 +10991,13 @@
         <v>28</v>
       </c>
       <c r="S146">
-        <v>4417332</v>
+        <v>1683449</v>
       </c>
       <c r="T146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>19</v>
       </c>
@@ -11041,7 +11059,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>19</v>
       </c>
@@ -11103,7 +11121,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>19</v>
       </c>
@@ -11165,7 +11183,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -11227,7 +11245,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>19</v>
       </c>
@@ -11289,7 +11307,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>19</v>
       </c>
@@ -11351,7 +11369,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>19</v>
       </c>
@@ -11421,10 +11439,10 @@
         <v>8</v>
       </c>
       <c r="C154">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D154" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E154" t="s">
         <v>369</v>
@@ -11433,19 +11451,19 @@
         <v>370</v>
       </c>
       <c r="G154">
-        <v>6275905</v>
+        <v>6275909</v>
       </c>
       <c r="H154" t="s">
         <v>23</v>
       </c>
       <c r="I154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J154">
         <v>4</v>
       </c>
       <c r="K154">
-        <v>6275905</v>
+        <v>6275909</v>
       </c>
       <c r="L154" t="s">
         <v>24</v>
@@ -11469,10 +11487,10 @@
         <v>28</v>
       </c>
       <c r="S154">
-        <v>5791023</v>
+        <v>1542401</v>
       </c>
       <c r="T154">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.35">
@@ -11495,19 +11513,19 @@
         <v>370</v>
       </c>
       <c r="G155">
-        <v>6275908</v>
+        <v>6275905</v>
       </c>
       <c r="H155" t="s">
         <v>23</v>
       </c>
       <c r="I155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J155">
         <v>4</v>
       </c>
       <c r="K155">
-        <v>6275908</v>
+        <v>6275905</v>
       </c>
       <c r="L155" t="s">
         <v>24</v>
@@ -11531,10 +11549,10 @@
         <v>28</v>
       </c>
       <c r="S155">
-        <v>1683449</v>
+        <v>5791023</v>
       </c>
       <c r="T155">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.35">
@@ -11557,19 +11575,19 @@
         <v>370</v>
       </c>
       <c r="G156">
-        <v>6275909</v>
+        <v>6275908</v>
       </c>
       <c r="H156" t="s">
         <v>23</v>
       </c>
       <c r="I156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J156">
         <v>4</v>
       </c>
       <c r="K156">
-        <v>6275909</v>
+        <v>6275908</v>
       </c>
       <c r="L156" t="s">
         <v>24</v>
@@ -11593,7 +11611,7 @@
         <v>28</v>
       </c>
       <c r="S156">
-        <v>1542401</v>
+        <v>1683449</v>
       </c>
       <c r="T156">
         <v>3</v>
@@ -11613,31 +11631,31 @@
         <v>41</v>
       </c>
       <c r="E157" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G157">
-        <v>6275906</v>
+        <v>6275909</v>
       </c>
       <c r="H157" t="s">
         <v>23</v>
       </c>
       <c r="I157">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J157">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K157">
-        <v>6275906</v>
+        <v>6275909</v>
       </c>
       <c r="L157" t="s">
         <v>24</v>
       </c>
       <c r="M157">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -11646,7 +11664,7 @@
         <v>2</v>
       </c>
       <c r="P157">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -11655,10 +11673,10 @@
         <v>28</v>
       </c>
       <c r="S157">
-        <v>2662315</v>
+        <v>1542401</v>
       </c>
       <c r="T157">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.35">
@@ -11669,19 +11687,19 @@
         <v>8</v>
       </c>
       <c r="C158">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D158" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E158" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G158">
-        <v>6275910</v>
+        <v>6275908</v>
       </c>
       <c r="H158" t="s">
         <v>23</v>
@@ -11690,16 +11708,16 @@
         <v>2</v>
       </c>
       <c r="J158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K158">
-        <v>6275910</v>
+        <v>6275908</v>
       </c>
       <c r="L158" t="s">
         <v>24</v>
       </c>
       <c r="M158">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -11708,7 +11726,7 @@
         <v>2</v>
       </c>
       <c r="P158">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -11717,10 +11735,10 @@
         <v>28</v>
       </c>
       <c r="S158">
-        <v>2475800</v>
+        <v>1683449</v>
       </c>
       <c r="T158">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.35">
@@ -11731,19 +11749,19 @@
         <v>8</v>
       </c>
       <c r="C159">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D159" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E159" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F159" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G159">
-        <v>6275911</v>
+        <v>6275909</v>
       </c>
       <c r="H159" t="s">
         <v>23</v>
@@ -11752,16 +11770,16 @@
         <v>3</v>
       </c>
       <c r="J159">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K159">
-        <v>6275911</v>
+        <v>6275909</v>
       </c>
       <c r="L159" t="s">
         <v>24</v>
       </c>
       <c r="M159">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N159">
         <v>0</v>
@@ -11770,7 +11788,7 @@
         <v>2</v>
       </c>
       <c r="P159">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -11779,13 +11797,13 @@
         <v>28</v>
       </c>
       <c r="S159">
-        <v>1138064</v>
+        <v>1542401</v>
       </c>
       <c r="T159">
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>19</v>
       </c>
@@ -11847,7 +11865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>19</v>
       </c>
@@ -11909,7 +11927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>19</v>
       </c>
@@ -11971,7 +11989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>19</v>
       </c>
@@ -12033,7 +12051,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>19</v>
       </c>
@@ -12095,7 +12113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>19</v>
       </c>
@@ -12157,7 +12175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>19</v>
       </c>
@@ -12219,7 +12237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>19</v>
       </c>
@@ -12281,7 +12299,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>19</v>
       </c>
@@ -12343,7 +12361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>19</v>
       </c>
@@ -12405,7 +12423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>19</v>
       </c>
@@ -12467,7 +12485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>19</v>
       </c>
@@ -12529,7 +12547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>19</v>
       </c>
@@ -12591,7 +12609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>19</v>
       </c>
@@ -12653,7 +12671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>19</v>
       </c>
@@ -12715,7 +12733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>19</v>
       </c>
@@ -12785,19 +12803,19 @@
         <v>8</v>
       </c>
       <c r="C176">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D176" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E176" t="s">
-        <v>425</v>
+        <v>369</v>
       </c>
       <c r="F176" t="s">
-        <v>426</v>
+        <v>370</v>
       </c>
       <c r="G176">
-        <v>6275912</v>
+        <v>6275908</v>
       </c>
       <c r="H176" t="s">
         <v>23</v>
@@ -12806,25 +12824,25 @@
         <v>2</v>
       </c>
       <c r="J176">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K176">
-        <v>6275912</v>
+        <v>6275908</v>
       </c>
       <c r="L176" t="s">
         <v>24</v>
       </c>
       <c r="M176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N176">
         <v>0</v>
       </c>
       <c r="O176">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -12833,7 +12851,7 @@
         <v>28</v>
       </c>
       <c r="S176">
-        <v>1702715</v>
+        <v>1683449</v>
       </c>
       <c r="T176">
         <v>2</v>
@@ -12847,46 +12865,46 @@
         <v>8</v>
       </c>
       <c r="C177">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D177" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E177" t="s">
-        <v>425</v>
+        <v>369</v>
       </c>
       <c r="F177" t="s">
-        <v>426</v>
+        <v>370</v>
       </c>
       <c r="G177">
-        <v>6275914</v>
+        <v>6275909</v>
       </c>
       <c r="H177" t="s">
         <v>23</v>
       </c>
       <c r="I177">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J177">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K177">
-        <v>6275914</v>
+        <v>6275909</v>
       </c>
       <c r="L177" t="s">
         <v>24</v>
       </c>
       <c r="M177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N177">
         <v>0</v>
       </c>
       <c r="O177">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -12895,13 +12913,13 @@
         <v>28</v>
       </c>
       <c r="S177">
-        <v>2072001</v>
+        <v>1542401</v>
       </c>
       <c r="T177">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>19</v>
       </c>
@@ -12963,7 +12981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>19</v>
       </c>
@@ -13025,7 +13043,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>19</v>
       </c>
@@ -13087,7 +13105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>19</v>
       </c>
@@ -13149,7 +13167,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>19</v>
       </c>
@@ -13219,19 +13237,19 @@
         <v>8</v>
       </c>
       <c r="C183">
-        <v>37</v>
+        <v>808</v>
       </c>
       <c r="D183" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E183" t="s">
-        <v>464</v>
+        <v>369</v>
       </c>
       <c r="F183" t="s">
-        <v>465</v>
+        <v>370</v>
       </c>
       <c r="G183">
-        <v>6291558</v>
+        <v>6275908</v>
       </c>
       <c r="H183" t="s">
         <v>23</v>
@@ -13240,25 +13258,25 @@
         <v>2</v>
       </c>
       <c r="J183">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K183">
-        <v>6291558</v>
+        <v>6275908</v>
       </c>
       <c r="L183" t="s">
         <v>24</v>
       </c>
       <c r="M183">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N183">
         <v>0</v>
       </c>
       <c r="O183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P183">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -13267,13 +13285,13 @@
         <v>28</v>
       </c>
       <c r="S183">
-        <v>1833141</v>
+        <v>1683449</v>
       </c>
       <c r="T183">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>19</v>
       </c>
@@ -13343,61 +13361,61 @@
         <v>8</v>
       </c>
       <c r="C185">
-        <v>37</v>
+        <v>808</v>
       </c>
       <c r="D185" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E185" t="s">
-        <v>479</v>
+        <v>369</v>
       </c>
       <c r="F185" t="s">
-        <v>480</v>
+        <v>370</v>
       </c>
       <c r="G185">
-        <v>6269607</v>
+        <v>6275909</v>
       </c>
       <c r="H185" t="s">
         <v>23</v>
       </c>
       <c r="I185">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J185">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K185">
-        <v>6269607</v>
+        <v>6275909</v>
       </c>
       <c r="L185" t="s">
         <v>24</v>
       </c>
       <c r="M185">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N185">
         <v>0</v>
       </c>
       <c r="O185">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P185">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q185">
         <v>0</v>
       </c>
       <c r="R185" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S185">
-        <v>1992818</v>
+        <v>1542401</v>
       </c>
       <c r="T185">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>19</v>
       </c>
@@ -13459,7 +13477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>19</v>
       </c>
@@ -13529,37 +13547,37 @@
         <v>8</v>
       </c>
       <c r="C188">
-        <v>38</v>
+        <v>1040</v>
       </c>
       <c r="D188" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E188" t="s">
-        <v>53</v>
+        <v>369</v>
       </c>
       <c r="F188" t="s">
-        <v>54</v>
+        <v>370</v>
       </c>
       <c r="G188">
-        <v>6285584</v>
+        <v>6275908</v>
       </c>
       <c r="H188" t="s">
         <v>23</v>
       </c>
       <c r="I188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J188">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K188">
-        <v>6285584</v>
+        <v>6275908</v>
       </c>
       <c r="L188" t="s">
         <v>24</v>
       </c>
       <c r="M188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N188">
         <v>0</v>
@@ -13568,22 +13586,22 @@
         <v>2</v>
       </c>
       <c r="P188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q188">
         <v>0</v>
       </c>
       <c r="R188" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S188">
-        <v>1145553</v>
+        <v>1683449</v>
       </c>
       <c r="T188">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>19</v>
       </c>
@@ -13645,7 +13663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>19</v>
       </c>
@@ -13707,7 +13725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>19</v>
       </c>
@@ -13769,7 +13787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>19</v>
       </c>
@@ -13831,7 +13849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>19</v>
       </c>
@@ -13893,7 +13911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>19</v>
       </c>
@@ -13955,7 +13973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>19</v>
       </c>
@@ -14017,7 +14035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>19</v>
       </c>
@@ -14079,7 +14097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>19</v>
       </c>
@@ -14141,7 +14159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>19</v>
       </c>
@@ -14203,7 +14221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>19</v>
       </c>
@@ -14265,7 +14283,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>19</v>
       </c>
@@ -14335,46 +14353,46 @@
         <v>8</v>
       </c>
       <c r="C201">
-        <v>38</v>
+        <v>1040</v>
       </c>
       <c r="D201" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E201" t="s">
-        <v>204</v>
+        <v>369</v>
       </c>
       <c r="F201" t="s">
-        <v>205</v>
+        <v>370</v>
       </c>
       <c r="G201">
-        <v>6291544</v>
+        <v>6275909</v>
       </c>
       <c r="H201" t="s">
         <v>23</v>
       </c>
       <c r="I201">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J201">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K201">
-        <v>6291544</v>
+        <v>6275909</v>
       </c>
       <c r="L201" t="s">
         <v>24</v>
       </c>
       <c r="M201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N201">
         <v>0</v>
       </c>
       <c r="O201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P201">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -14383,13 +14401,13 @@
         <v>28</v>
       </c>
       <c r="S201">
-        <v>1295362</v>
+        <v>1542401</v>
       </c>
       <c r="T201">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>19</v>
       </c>
@@ -14451,7 +14469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>19</v>
       </c>
@@ -14521,19 +14539,19 @@
         <v>8</v>
       </c>
       <c r="C204">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D204" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E204" t="s">
-        <v>275</v>
+        <v>371</v>
       </c>
       <c r="F204" t="s">
-        <v>276</v>
+        <v>372</v>
       </c>
       <c r="G204">
-        <v>6274499</v>
+        <v>6275906</v>
       </c>
       <c r="H204" t="s">
         <v>23</v>
@@ -14542,10 +14560,10 @@
         <v>1</v>
       </c>
       <c r="J204">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K204">
-        <v>6274499</v>
+        <v>6275906</v>
       </c>
       <c r="L204" t="s">
         <v>24</v>
@@ -14557,7 +14575,7 @@
         <v>0</v>
       </c>
       <c r="O204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P204">
         <v>2</v>
@@ -14566,16 +14584,16 @@
         <v>0</v>
       </c>
       <c r="R204" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S204">
-        <v>4339346</v>
+        <v>2662315</v>
       </c>
       <c r="T204">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>19</v>
       </c>
@@ -14637,7 +14655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>19</v>
       </c>
@@ -14699,7 +14717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>19</v>
       </c>
@@ -14761,7 +14779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>19</v>
       </c>
@@ -14823,7 +14841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>19</v>
       </c>
@@ -14885,7 +14903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>19</v>
       </c>
@@ -14947,7 +14965,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>19</v>
       </c>
@@ -15009,7 +15027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>19</v>
       </c>
@@ -15071,7 +15089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>19</v>
       </c>
@@ -15133,7 +15151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>19</v>
       </c>
@@ -15195,7 +15213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>19</v>
       </c>
@@ -15257,7 +15275,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>19</v>
       </c>
@@ -15319,7 +15337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>19</v>
       </c>
@@ -15389,31 +15407,31 @@
         <v>8</v>
       </c>
       <c r="C218">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D218" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E218" t="s">
-        <v>479</v>
+        <v>371</v>
       </c>
       <c r="F218" t="s">
-        <v>480</v>
+        <v>372</v>
       </c>
       <c r="G218">
-        <v>6282337</v>
+        <v>6275910</v>
       </c>
       <c r="H218" t="s">
         <v>23</v>
       </c>
       <c r="I218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J218">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K218">
-        <v>6282337</v>
+        <v>6275910</v>
       </c>
       <c r="L218" t="s">
         <v>24</v>
@@ -15425,7 +15443,7 @@
         <v>0</v>
       </c>
       <c r="O218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P218">
         <v>2</v>
@@ -15434,16 +15452,16 @@
         <v>0</v>
       </c>
       <c r="R218" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S218">
-        <v>2782610</v>
+        <v>2475800</v>
       </c>
       <c r="T218">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>19</v>
       </c>
@@ -15505,7 +15523,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>19</v>
       </c>
@@ -15567,7 +15585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>19</v>
       </c>
@@ -15629,7 +15647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>19</v>
       </c>
@@ -15691,7 +15709,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>19</v>
       </c>
@@ -15761,31 +15779,31 @@
         <v>8</v>
       </c>
       <c r="C224">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D224" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E224" t="s">
-        <v>53</v>
+        <v>371</v>
       </c>
       <c r="F224" t="s">
-        <v>54</v>
+        <v>372</v>
       </c>
       <c r="G224">
-        <v>6279383</v>
+        <v>6275911</v>
       </c>
       <c r="H224" t="s">
         <v>23</v>
       </c>
       <c r="I224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K224">
-        <v>6279383</v>
+        <v>6275911</v>
       </c>
       <c r="L224" t="s">
         <v>24</v>
@@ -15797,7 +15815,7 @@
         <v>0</v>
       </c>
       <c r="O224">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P224">
         <v>2</v>
@@ -15806,16 +15824,16 @@
         <v>0</v>
       </c>
       <c r="R224" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S224">
-        <v>2826511</v>
+        <v>1138064</v>
       </c>
       <c r="T224">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>19</v>
       </c>
@@ -15877,7 +15895,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>19</v>
       </c>
@@ -15939,7 +15957,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>19</v>
       </c>
@@ -16001,7 +16019,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>19</v>
       </c>
@@ -16063,7 +16081,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>19</v>
       </c>
@@ -16125,7 +16143,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>19</v>
       </c>
@@ -16187,7 +16205,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>19</v>
       </c>
@@ -16249,7 +16267,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>19</v>
       </c>
@@ -16311,7 +16329,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>19</v>
       </c>
@@ -16373,7 +16391,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>19</v>
       </c>
@@ -16435,7 +16453,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>19</v>
       </c>
@@ -16497,7 +16515,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>19</v>
       </c>
@@ -16559,7 +16577,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>19</v>
       </c>
@@ -16621,7 +16639,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -16683,7 +16701,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>19</v>
       </c>
@@ -16745,7 +16763,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>19</v>
       </c>
@@ -16807,7 +16825,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>19</v>
       </c>
@@ -16869,7 +16887,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>19</v>
       </c>
@@ -16931,7 +16949,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>19</v>
       </c>
@@ -16993,7 +17011,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>19</v>
       </c>
@@ -17055,7 +17073,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>19</v>
       </c>
@@ -17117,7 +17135,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>19</v>
       </c>
@@ -17179,7 +17197,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>19</v>
       </c>
@@ -17241,7 +17259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>19</v>
       </c>
@@ -17303,7 +17321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>19</v>
       </c>
@@ -17365,7 +17383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>19</v>
       </c>
@@ -17427,7 +17445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>19</v>
       </c>
@@ -17489,7 +17507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>19</v>
       </c>
@@ -17551,7 +17569,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>19</v>
       </c>
@@ -17613,7 +17631,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>19</v>
       </c>
@@ -17675,7 +17693,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>19</v>
       </c>
@@ -17737,7 +17755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>19</v>
       </c>
@@ -17799,7 +17817,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>19</v>
       </c>
@@ -17861,7 +17879,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>19</v>
       </c>
@@ -17923,7 +17941,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>19</v>
       </c>
@@ -17985,7 +18003,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>19</v>
       </c>
@@ -18047,7 +18065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>19</v>
       </c>
@@ -18109,7 +18127,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>19</v>
       </c>
@@ -18171,7 +18189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>19</v>
       </c>
@@ -18233,7 +18251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>19</v>
       </c>
@@ -18295,7 +18313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>19</v>
       </c>
@@ -18357,7 +18375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>19</v>
       </c>
@@ -18419,7 +18437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>19</v>
       </c>
@@ -18481,7 +18499,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>19</v>
       </c>
@@ -18551,37 +18569,37 @@
         <v>8</v>
       </c>
       <c r="C269">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D269" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E269" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F269" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G269">
-        <v>6275908</v>
+        <v>6275906</v>
       </c>
       <c r="H269" t="s">
         <v>23</v>
       </c>
       <c r="I269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J269">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K269">
-        <v>6275908</v>
+        <v>6275906</v>
       </c>
       <c r="L269" t="s">
         <v>24</v>
       </c>
       <c r="M269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N269">
         <v>0</v>
@@ -18590,7 +18608,7 @@
         <v>2</v>
       </c>
       <c r="P269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -18599,10 +18617,10 @@
         <v>28</v>
       </c>
       <c r="S269">
-        <v>1683449</v>
+        <v>2662315</v>
       </c>
       <c r="T269">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:20" x14ac:dyDescent="0.35">
@@ -18613,37 +18631,37 @@
         <v>8</v>
       </c>
       <c r="C270">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D270" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E270" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F270" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G270">
-        <v>6275909</v>
+        <v>6275910</v>
       </c>
       <c r="H270" t="s">
         <v>23</v>
       </c>
       <c r="I270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J270">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K270">
-        <v>6275909</v>
+        <v>6275910</v>
       </c>
       <c r="L270" t="s">
         <v>24</v>
       </c>
       <c r="M270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N270">
         <v>0</v>
@@ -18652,7 +18670,7 @@
         <v>2</v>
       </c>
       <c r="P270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -18661,10 +18679,10 @@
         <v>28</v>
       </c>
       <c r="S270">
-        <v>1542401</v>
+        <v>2475800</v>
       </c>
       <c r="T270">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="271" spans="1:20" x14ac:dyDescent="0.35">
@@ -18675,10 +18693,10 @@
         <v>8</v>
       </c>
       <c r="C271">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D271" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E271" t="s">
         <v>371</v>
@@ -18687,19 +18705,19 @@
         <v>372</v>
       </c>
       <c r="G271">
-        <v>6275906</v>
+        <v>6275911</v>
       </c>
       <c r="H271" t="s">
         <v>23</v>
       </c>
       <c r="I271">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J271">
         <v>3</v>
       </c>
       <c r="K271">
-        <v>6275906</v>
+        <v>6275911</v>
       </c>
       <c r="L271" t="s">
         <v>24</v>
@@ -18723,10 +18741,10 @@
         <v>28</v>
       </c>
       <c r="S271">
-        <v>2662315</v>
+        <v>1138064</v>
       </c>
       <c r="T271">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272" spans="1:20" x14ac:dyDescent="0.35">
@@ -18749,19 +18767,19 @@
         <v>372</v>
       </c>
       <c r="G272">
-        <v>6275910</v>
+        <v>6275906</v>
       </c>
       <c r="H272" t="s">
         <v>23</v>
       </c>
       <c r="I272">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J272">
         <v>3</v>
       </c>
       <c r="K272">
-        <v>6275910</v>
+        <v>6275906</v>
       </c>
       <c r="L272" t="s">
         <v>24</v>
@@ -18785,10 +18803,10 @@
         <v>28</v>
       </c>
       <c r="S272">
-        <v>2475800</v>
+        <v>2662315</v>
       </c>
       <c r="T272">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:20" x14ac:dyDescent="0.35">
@@ -18811,19 +18829,19 @@
         <v>372</v>
       </c>
       <c r="G273">
-        <v>6275911</v>
+        <v>6275910</v>
       </c>
       <c r="H273" t="s">
         <v>23</v>
       </c>
       <c r="I273">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J273">
         <v>3</v>
       </c>
       <c r="K273">
-        <v>6275911</v>
+        <v>6275910</v>
       </c>
       <c r="L273" t="s">
         <v>24</v>
@@ -18847,10 +18865,10 @@
         <v>28</v>
       </c>
       <c r="S273">
-        <v>1138064</v>
+        <v>2475800</v>
       </c>
       <c r="T273">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:20" x14ac:dyDescent="0.35">
@@ -18867,40 +18885,40 @@
         <v>36</v>
       </c>
       <c r="E274" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F274" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G274">
-        <v>6287671</v>
+        <v>6275911</v>
       </c>
       <c r="H274" t="s">
         <v>23</v>
       </c>
       <c r="I274">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J274">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K274">
-        <v>6287671</v>
+        <v>6275911</v>
       </c>
       <c r="L274" t="s">
         <v>24</v>
       </c>
       <c r="M274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N274">
         <v>0</v>
       </c>
       <c r="O274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -18909,13 +18927,13 @@
         <v>28</v>
       </c>
       <c r="S274">
-        <v>1609406</v>
+        <v>1138064</v>
       </c>
       <c r="T274">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>19</v>
       </c>
@@ -18977,7 +18995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>19</v>
       </c>
@@ -19039,7 +19057,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>19</v>
       </c>
@@ -19101,7 +19119,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>19</v>
       </c>
@@ -19163,7 +19181,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>19</v>
       </c>
@@ -19225,7 +19243,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>19</v>
       </c>
@@ -19287,7 +19305,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>19</v>
       </c>
@@ -19349,7 +19367,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>19</v>
       </c>
@@ -19411,7 +19429,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>19</v>
       </c>
@@ -19473,7 +19491,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>19</v>
       </c>
@@ -19543,19 +19561,19 @@
         <v>8</v>
       </c>
       <c r="C285">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D285" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E285" t="s">
-        <v>425</v>
+        <v>371</v>
       </c>
       <c r="F285" t="s">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="G285">
-        <v>6275907</v>
+        <v>6275906</v>
       </c>
       <c r="H285" t="s">
         <v>23</v>
@@ -19567,7 +19585,7 @@
         <v>3</v>
       </c>
       <c r="K285">
-        <v>6275907</v>
+        <v>6275906</v>
       </c>
       <c r="L285" t="s">
         <v>24</v>
@@ -19579,7 +19597,7 @@
         <v>0</v>
       </c>
       <c r="O285">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P285">
         <v>2</v>
@@ -19591,10 +19609,10 @@
         <v>28</v>
       </c>
       <c r="S285">
-        <v>3003404</v>
+        <v>2662315</v>
       </c>
       <c r="T285">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:20" x14ac:dyDescent="0.35">
@@ -19605,19 +19623,19 @@
         <v>8</v>
       </c>
       <c r="C286">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D286" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E286" t="s">
-        <v>425</v>
+        <v>371</v>
       </c>
       <c r="F286" t="s">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="G286">
-        <v>6275912</v>
+        <v>6275910</v>
       </c>
       <c r="H286" t="s">
         <v>23</v>
@@ -19629,7 +19647,7 @@
         <v>3</v>
       </c>
       <c r="K286">
-        <v>6275912</v>
+        <v>6275910</v>
       </c>
       <c r="L286" t="s">
         <v>24</v>
@@ -19641,7 +19659,7 @@
         <v>0</v>
       </c>
       <c r="O286">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P286">
         <v>2</v>
@@ -19653,10 +19671,10 @@
         <v>28</v>
       </c>
       <c r="S286">
-        <v>1702715</v>
+        <v>2475800</v>
       </c>
       <c r="T286">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287" spans="1:20" x14ac:dyDescent="0.35">
@@ -19667,19 +19685,19 @@
         <v>8</v>
       </c>
       <c r="C287">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D287" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E287" t="s">
-        <v>425</v>
+        <v>371</v>
       </c>
       <c r="F287" t="s">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="G287">
-        <v>6275913</v>
+        <v>6275911</v>
       </c>
       <c r="H287" t="s">
         <v>23</v>
@@ -19691,7 +19709,7 @@
         <v>3</v>
       </c>
       <c r="K287">
-        <v>6275913</v>
+        <v>6275911</v>
       </c>
       <c r="L287" t="s">
         <v>24</v>
@@ -19703,7 +19721,7 @@
         <v>0</v>
       </c>
       <c r="O287">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P287">
         <v>2</v>
@@ -19715,10 +19733,10 @@
         <v>28</v>
       </c>
       <c r="S287">
-        <v>2471821</v>
+        <v>1138064</v>
       </c>
       <c r="T287">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:20" x14ac:dyDescent="0.35">
@@ -19729,31 +19747,31 @@
         <v>8</v>
       </c>
       <c r="C288">
-        <v>39</v>
+        <v>1040</v>
       </c>
       <c r="D288" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E288" t="s">
-        <v>479</v>
+        <v>371</v>
       </c>
       <c r="F288" t="s">
-        <v>480</v>
+        <v>372</v>
       </c>
       <c r="G288">
-        <v>6279390</v>
+        <v>6275910</v>
       </c>
       <c r="H288" t="s">
         <v>23</v>
       </c>
       <c r="I288">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J288">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K288">
-        <v>6279390</v>
+        <v>6275910</v>
       </c>
       <c r="L288" t="s">
         <v>24</v>
@@ -19765,7 +19783,7 @@
         <v>0</v>
       </c>
       <c r="O288">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P288">
         <v>2</v>
@@ -19774,16 +19792,16 @@
         <v>0</v>
       </c>
       <c r="R288" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S288">
-        <v>2615883</v>
+        <v>2475800</v>
       </c>
       <c r="T288">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>19</v>
       </c>
@@ -19845,7 +19863,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>19</v>
       </c>
@@ -19915,31 +19933,31 @@
         <v>8</v>
       </c>
       <c r="C291">
-        <v>40</v>
+        <v>1040</v>
       </c>
       <c r="D291" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E291" t="s">
-        <v>53</v>
+        <v>371</v>
       </c>
       <c r="F291" t="s">
-        <v>54</v>
+        <v>372</v>
       </c>
       <c r="G291">
-        <v>6285519</v>
+        <v>6275911</v>
       </c>
       <c r="H291" t="s">
         <v>23</v>
       </c>
       <c r="I291">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J291">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K291">
-        <v>6285519</v>
+        <v>6275911</v>
       </c>
       <c r="L291" t="s">
         <v>24</v>
@@ -19951,7 +19969,7 @@
         <v>0</v>
       </c>
       <c r="O291">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P291">
         <v>2</v>
@@ -19960,16 +19978,16 @@
         <v>0</v>
       </c>
       <c r="R291" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S291">
-        <v>2047115</v>
+        <v>1138064</v>
       </c>
       <c r="T291">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>19</v>
       </c>
@@ -20031,7 +20049,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>19</v>
       </c>
@@ -20093,7 +20111,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>19</v>
       </c>
@@ -20155,7 +20173,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>19</v>
       </c>
@@ -20217,7 +20235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>19</v>
       </c>
@@ -20279,7 +20297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>19</v>
       </c>
@@ -20341,7 +20359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>19</v>
       </c>
@@ -20403,7 +20421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>19</v>
       </c>
@@ -20465,7 +20483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>19</v>
       </c>
@@ -20527,7 +20545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>19</v>
       </c>
@@ -20589,7 +20607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>19</v>
       </c>
@@ -20651,7 +20669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>19</v>
       </c>
@@ -20713,7 +20731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>19</v>
       </c>
@@ -20775,7 +20793,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>19</v>
       </c>
@@ -20837,7 +20855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>19</v>
       </c>
@@ -20899,7 +20917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>19</v>
       </c>
@@ -20961,7 +20979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>19</v>
       </c>
@@ -21023,7 +21041,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>19</v>
       </c>
@@ -21085,7 +21103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>19</v>
       </c>
@@ -21147,7 +21165,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>19</v>
       </c>
@@ -21209,7 +21227,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>19</v>
       </c>
@@ -21271,7 +21289,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>19</v>
       </c>
@@ -21333,7 +21351,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>19</v>
       </c>
@@ -21395,7 +21413,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>19</v>
       </c>
@@ -21457,7 +21475,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>19</v>
       </c>
@@ -21519,7 +21537,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>19</v>
       </c>
@@ -21581,7 +21599,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>19</v>
       </c>
@@ -21643,7 +21661,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>19</v>
       </c>
@@ -21705,7 +21723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>19</v>
       </c>
@@ -21767,7 +21785,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>19</v>
       </c>
@@ -21829,7 +21847,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>19</v>
       </c>
@@ -21891,7 +21909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>19</v>
       </c>
@@ -21953,7 +21971,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>19</v>
       </c>
@@ -22015,7 +22033,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>19</v>
       </c>
@@ -22085,19 +22103,19 @@
         <v>8</v>
       </c>
       <c r="C326">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D326" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E326" t="s">
-        <v>275</v>
+        <v>425</v>
       </c>
       <c r="F326" t="s">
-        <v>276</v>
+        <v>426</v>
       </c>
       <c r="G326">
-        <v>6274499</v>
+        <v>6275907</v>
       </c>
       <c r="H326" t="s">
         <v>23</v>
@@ -22106,10 +22124,10 @@
         <v>1</v>
       </c>
       <c r="J326">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K326">
-        <v>6274499</v>
+        <v>6275907</v>
       </c>
       <c r="L326" t="s">
         <v>24</v>
@@ -22121,7 +22139,7 @@
         <v>0</v>
       </c>
       <c r="O326">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P326">
         <v>2</v>
@@ -22130,16 +22148,16 @@
         <v>0</v>
       </c>
       <c r="R326" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S326">
-        <v>4339346</v>
+        <v>3003404</v>
       </c>
       <c r="T326">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>19</v>
       </c>
@@ -22201,7 +22219,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>19</v>
       </c>
@@ -22263,7 +22281,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>19</v>
       </c>
@@ -22325,7 +22343,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>19</v>
       </c>
@@ -22387,7 +22405,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>19</v>
       </c>
@@ -22449,7 +22467,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>19</v>
       </c>
@@ -22519,46 +22537,46 @@
         <v>8</v>
       </c>
       <c r="C333">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D333" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E333" t="s">
-        <v>369</v>
+        <v>425</v>
       </c>
       <c r="F333" t="s">
-        <v>370</v>
+        <v>426</v>
       </c>
       <c r="G333">
-        <v>6275908</v>
+        <v>6275913</v>
       </c>
       <c r="H333" t="s">
         <v>23</v>
       </c>
       <c r="I333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J333">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K333">
-        <v>6275908</v>
+        <v>6275913</v>
       </c>
       <c r="L333" t="s">
         <v>24</v>
       </c>
       <c r="M333">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N333">
         <v>0</v>
       </c>
       <c r="O333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P333">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -22567,7 +22585,7 @@
         <v>28</v>
       </c>
       <c r="S333">
-        <v>1683449</v>
+        <v>2471821</v>
       </c>
       <c r="T333">
         <v>2</v>
@@ -22581,46 +22599,46 @@
         <v>8</v>
       </c>
       <c r="C334">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D334" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E334" t="s">
-        <v>369</v>
+        <v>425</v>
       </c>
       <c r="F334" t="s">
-        <v>370</v>
+        <v>426</v>
       </c>
       <c r="G334">
-        <v>6275909</v>
+        <v>6275915</v>
       </c>
       <c r="H334" t="s">
         <v>23</v>
       </c>
       <c r="I334">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J334">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K334">
-        <v>6275909</v>
+        <v>6275915</v>
       </c>
       <c r="L334" t="s">
         <v>24</v>
       </c>
       <c r="M334">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N334">
         <v>0</v>
       </c>
       <c r="O334">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P334">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -22629,10 +22647,10 @@
         <v>28</v>
       </c>
       <c r="S334">
-        <v>1542401</v>
+        <v>3002026</v>
       </c>
       <c r="T334">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:20" x14ac:dyDescent="0.35">
@@ -22643,31 +22661,31 @@
         <v>8</v>
       </c>
       <c r="C335">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D335" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E335" t="s">
-        <v>371</v>
+        <v>425</v>
       </c>
       <c r="F335" t="s">
-        <v>372</v>
+        <v>426</v>
       </c>
       <c r="G335">
-        <v>6275906</v>
+        <v>6275912</v>
       </c>
       <c r="H335" t="s">
         <v>23</v>
       </c>
       <c r="I335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J335">
         <v>3</v>
       </c>
       <c r="K335">
-        <v>6275906</v>
+        <v>6275912</v>
       </c>
       <c r="L335" t="s">
         <v>24</v>
@@ -22679,7 +22697,7 @@
         <v>0</v>
       </c>
       <c r="O335">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P335">
         <v>2</v>
@@ -22691,10 +22709,10 @@
         <v>28</v>
       </c>
       <c r="S335">
-        <v>2662315</v>
+        <v>1702715</v>
       </c>
       <c r="T335">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336" spans="1:20" x14ac:dyDescent="0.35">
@@ -22705,31 +22723,31 @@
         <v>8</v>
       </c>
       <c r="C336">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D336" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E336" t="s">
-        <v>371</v>
+        <v>425</v>
       </c>
       <c r="F336" t="s">
-        <v>372</v>
+        <v>426</v>
       </c>
       <c r="G336">
-        <v>6275910</v>
+        <v>6275914</v>
       </c>
       <c r="H336" t="s">
         <v>23</v>
       </c>
       <c r="I336">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J336">
         <v>3</v>
       </c>
       <c r="K336">
-        <v>6275910</v>
+        <v>6275914</v>
       </c>
       <c r="L336" t="s">
         <v>24</v>
@@ -22741,7 +22759,7 @@
         <v>0</v>
       </c>
       <c r="O336">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P336">
         <v>2</v>
@@ -22753,7 +22771,7 @@
         <v>28</v>
       </c>
       <c r="S336">
-        <v>2475800</v>
+        <v>2072001</v>
       </c>
       <c r="T336">
         <v>1</v>
@@ -22767,31 +22785,31 @@
         <v>8</v>
       </c>
       <c r="C337">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D337" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E337" t="s">
-        <v>371</v>
+        <v>425</v>
       </c>
       <c r="F337" t="s">
-        <v>372</v>
+        <v>426</v>
       </c>
       <c r="G337">
-        <v>6275911</v>
+        <v>6275907</v>
       </c>
       <c r="H337" t="s">
         <v>23</v>
       </c>
       <c r="I337">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J337">
         <v>3</v>
       </c>
       <c r="K337">
-        <v>6275911</v>
+        <v>6275907</v>
       </c>
       <c r="L337" t="s">
         <v>24</v>
@@ -22803,7 +22821,7 @@
         <v>0</v>
       </c>
       <c r="O337">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P337">
         <v>2</v>
@@ -22815,13 +22833,13 @@
         <v>28</v>
       </c>
       <c r="S337">
-        <v>1138064</v>
+        <v>3003404</v>
       </c>
       <c r="T337">
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>19</v>
       </c>
@@ -22883,7 +22901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>19</v>
       </c>
@@ -22945,7 +22963,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>19</v>
       </c>
@@ -23007,7 +23025,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>19</v>
       </c>
@@ -23077,10 +23095,10 @@
         <v>8</v>
       </c>
       <c r="C342">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D342" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E342" t="s">
         <v>425</v>
@@ -23089,19 +23107,19 @@
         <v>426</v>
       </c>
       <c r="G342">
-        <v>6275907</v>
+        <v>6275912</v>
       </c>
       <c r="H342" t="s">
         <v>23</v>
       </c>
       <c r="I342">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J342">
         <v>3</v>
       </c>
       <c r="K342">
-        <v>6275907</v>
+        <v>6275912</v>
       </c>
       <c r="L342" t="s">
         <v>24</v>
@@ -23125,10 +23143,10 @@
         <v>28</v>
       </c>
       <c r="S342">
-        <v>3003404</v>
+        <v>1702715</v>
       </c>
       <c r="T342">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343" spans="1:20" x14ac:dyDescent="0.35">
@@ -23139,10 +23157,10 @@
         <v>8</v>
       </c>
       <c r="C343">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D343" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E343" t="s">
         <v>425</v>
@@ -23190,10 +23208,10 @@
         <v>2471821</v>
       </c>
       <c r="T343">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>19</v>
       </c>
@@ -23255,7 +23273,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>19</v>
       </c>
@@ -23317,7 +23335,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>19</v>
       </c>
@@ -23379,7 +23397,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>19</v>
       </c>
@@ -23441,7 +23459,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>19</v>
       </c>
@@ -23503,7 +23521,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>19</v>
       </c>
@@ -23579,13 +23597,13 @@
         <v>29</v>
       </c>
       <c r="E350" t="s">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="F350" t="s">
-        <v>480</v>
+        <v>426</v>
       </c>
       <c r="G350">
-        <v>6282339</v>
+        <v>6275907</v>
       </c>
       <c r="H350" t="s">
         <v>23</v>
@@ -23594,10 +23612,10 @@
         <v>1</v>
       </c>
       <c r="J350">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K350">
-        <v>6282339</v>
+        <v>6275907</v>
       </c>
       <c r="L350" t="s">
         <v>24</v>
@@ -23609,7 +23627,7 @@
         <v>0</v>
       </c>
       <c r="O350">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P350">
         <v>2</v>
@@ -23618,16 +23636,16 @@
         <v>0</v>
       </c>
       <c r="R350" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S350">
-        <v>1032729</v>
+        <v>3003404</v>
       </c>
       <c r="T350">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>19</v>
       </c>
@@ -23689,7 +23707,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>19</v>
       </c>
@@ -23751,7 +23769,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>19</v>
       </c>
@@ -23813,7 +23831,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>19</v>
       </c>
@@ -23883,31 +23901,31 @@
         <v>8</v>
       </c>
       <c r="C355">
-        <v>808</v>
+        <v>40</v>
       </c>
       <c r="D355" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E355" t="s">
-        <v>53</v>
+        <v>425</v>
       </c>
       <c r="F355" t="s">
-        <v>54</v>
+        <v>426</v>
       </c>
       <c r="G355">
-        <v>6279433</v>
+        <v>6275913</v>
       </c>
       <c r="H355" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="I355">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J355">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K355">
-        <v>6279433</v>
+        <v>6275913</v>
       </c>
       <c r="L355" t="s">
         <v>24</v>
@@ -23919,7 +23937,7 @@
         <v>0</v>
       </c>
       <c r="O355">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P355">
         <v>2</v>
@@ -23928,16 +23946,16 @@
         <v>0</v>
       </c>
       <c r="R355" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S355">
-        <v>4256585</v>
+        <v>2471821</v>
       </c>
       <c r="T355">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>19</v>
       </c>
@@ -23999,7 +24017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>19</v>
       </c>
@@ -24061,7 +24079,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>19</v>
       </c>
@@ -24123,7 +24141,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>19</v>
       </c>
@@ -24185,7 +24203,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>19</v>
       </c>
@@ -24247,7 +24265,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>19</v>
       </c>
@@ -24309,7 +24327,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>19</v>
       </c>
@@ -24371,7 +24389,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>19</v>
       </c>
@@ -24433,7 +24451,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>19</v>
       </c>
@@ -24495,7 +24513,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>19</v>
       </c>
@@ -24557,7 +24575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>19</v>
       </c>
@@ -24619,7 +24637,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>19</v>
       </c>
@@ -24681,7 +24699,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>19</v>
       </c>
@@ -24743,7 +24761,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>19</v>
       </c>
@@ -24805,7 +24823,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>19</v>
       </c>
@@ -24867,7 +24885,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>19</v>
       </c>
@@ -24929,7 +24947,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>19</v>
       </c>
@@ -24991,7 +25009,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>19</v>
       </c>
@@ -25053,7 +25071,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>19</v>
       </c>
@@ -25115,7 +25133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>19</v>
       </c>
@@ -25177,7 +25195,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>19</v>
       </c>
@@ -25239,7 +25257,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>19</v>
       </c>
@@ -25301,7 +25319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>19</v>
       </c>
@@ -25363,7 +25381,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>19</v>
       </c>
@@ -25425,7 +25443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>19</v>
       </c>
@@ -25487,7 +25505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>19</v>
       </c>
@@ -25549,7 +25567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>19</v>
       </c>
@@ -25611,7 +25629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>19</v>
       </c>
@@ -25673,7 +25691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>19</v>
       </c>
@@ -25735,7 +25753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>19</v>
       </c>
@@ -25797,7 +25815,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>19</v>
       </c>
@@ -25859,7 +25877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>19</v>
       </c>
@@ -25921,7 +25939,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>19</v>
       </c>
@@ -25983,7 +26001,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>19</v>
       </c>
@@ -26045,7 +26063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>19</v>
       </c>
@@ -26107,7 +26125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>19</v>
       </c>
@@ -26169,7 +26187,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>19</v>
       </c>
@@ -26231,7 +26249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>19</v>
       </c>
@@ -26293,7 +26311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>19</v>
       </c>
@@ -26355,7 +26373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>19</v>
       </c>
@@ -26417,7 +26435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>19</v>
       </c>
@@ -26479,7 +26497,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>19</v>
       </c>
@@ -26541,7 +26559,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>19</v>
       </c>
@@ -26617,40 +26635,40 @@
         <v>39</v>
       </c>
       <c r="E399" t="s">
-        <v>369</v>
+        <v>425</v>
       </c>
       <c r="F399" t="s">
-        <v>370</v>
+        <v>426</v>
       </c>
       <c r="G399">
-        <v>6275908</v>
+        <v>6275907</v>
       </c>
       <c r="H399" t="s">
         <v>23</v>
       </c>
       <c r="I399">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J399">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K399">
-        <v>6275908</v>
+        <v>6275907</v>
       </c>
       <c r="L399" t="s">
         <v>24</v>
       </c>
       <c r="M399">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N399">
         <v>0</v>
       </c>
       <c r="O399">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P399">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q399">
         <v>0</v>
@@ -26659,10 +26677,10 @@
         <v>28</v>
       </c>
       <c r="S399">
-        <v>1683449</v>
+        <v>3003404</v>
       </c>
       <c r="T399">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400" spans="1:20" x14ac:dyDescent="0.35">
@@ -26673,19 +26691,19 @@
         <v>8</v>
       </c>
       <c r="C400">
-        <v>808</v>
+        <v>1040</v>
       </c>
       <c r="D400" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E400" t="s">
-        <v>369</v>
+        <v>425</v>
       </c>
       <c r="F400" t="s">
-        <v>370</v>
+        <v>426</v>
       </c>
       <c r="G400">
-        <v>6275909</v>
+        <v>6275913</v>
       </c>
       <c r="H400" t="s">
         <v>23</v>
@@ -26694,25 +26712,25 @@
         <v>3</v>
       </c>
       <c r="J400">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K400">
-        <v>6275909</v>
+        <v>6275913</v>
       </c>
       <c r="L400" t="s">
         <v>24</v>
       </c>
       <c r="M400">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N400">
         <v>0</v>
       </c>
       <c r="O400">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P400">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q400">
         <v>0</v>
@@ -26721,13 +26739,13 @@
         <v>28</v>
       </c>
       <c r="S400">
-        <v>1542401</v>
+        <v>2471821</v>
       </c>
       <c r="T400">
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>19</v>
       </c>
@@ -26789,7 +26807,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>19</v>
       </c>
@@ -26851,7 +26869,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>19</v>
       </c>
@@ -26913,7 +26931,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>19</v>
       </c>
@@ -26975,7 +26993,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>19</v>
       </c>
@@ -27037,7 +27055,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>19</v>
       </c>
@@ -27099,7 +27117,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>19</v>
       </c>
@@ -27161,7 +27179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>19</v>
       </c>
@@ -27223,7 +27241,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>19</v>
       </c>
@@ -27293,19 +27311,19 @@
         <v>8</v>
       </c>
       <c r="C410">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D410" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E410" t="s">
-        <v>425</v>
+        <v>375</v>
       </c>
       <c r="F410" t="s">
-        <v>426</v>
+        <v>376</v>
       </c>
       <c r="G410">
-        <v>6275907</v>
+        <v>6287671</v>
       </c>
       <c r="H410" t="s">
         <v>23</v>
@@ -27314,16 +27332,16 @@
         <v>1</v>
       </c>
       <c r="J410">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K410">
-        <v>6275907</v>
+        <v>6287671</v>
       </c>
       <c r="L410" t="s">
         <v>24</v>
       </c>
       <c r="M410">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N410">
         <v>0</v>
@@ -27332,7 +27350,7 @@
         <v>3</v>
       </c>
       <c r="P410">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q410">
         <v>0</v>
@@ -27341,7 +27359,7 @@
         <v>28</v>
       </c>
       <c r="S410">
-        <v>3003404</v>
+        <v>1609406</v>
       </c>
       <c r="T410">
         <v>1</v>
@@ -27355,61 +27373,61 @@
         <v>8</v>
       </c>
       <c r="C411">
-        <v>808</v>
+        <v>1040</v>
       </c>
       <c r="D411" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E411" t="s">
-        <v>479</v>
+        <v>375</v>
       </c>
       <c r="F411" t="s">
-        <v>480</v>
+        <v>376</v>
       </c>
       <c r="G411">
-        <v>6279440</v>
+        <v>6287671</v>
       </c>
       <c r="H411" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="I411">
         <v>1</v>
       </c>
       <c r="J411">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K411">
-        <v>6279440</v>
+        <v>6287671</v>
       </c>
       <c r="L411" t="s">
         <v>24</v>
       </c>
       <c r="M411">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N411">
         <v>0</v>
       </c>
       <c r="O411">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P411">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q411">
         <v>0</v>
       </c>
       <c r="R411" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S411">
-        <v>1826282</v>
+        <v>1609406</v>
       </c>
       <c r="T411">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="412" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>19</v>
       </c>
@@ -27471,7 +27489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="413" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>19</v>
       </c>
@@ -27533,7 +27551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>19</v>
       </c>
@@ -27595,7 +27613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>19</v>
       </c>
@@ -27657,7 +27675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>19</v>
       </c>
@@ -27719,7 +27737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>19</v>
       </c>
@@ -27781,7 +27799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>19</v>
       </c>
@@ -27843,7 +27861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>19</v>
       </c>
@@ -27905,7 +27923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>19</v>
       </c>
@@ -27967,7 +27985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>19</v>
       </c>
@@ -28029,7 +28047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>19</v>
       </c>
@@ -28091,7 +28109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>19</v>
       </c>
@@ -28153,7 +28171,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="424" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>19</v>
       </c>
@@ -28215,7 +28233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="425" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>19</v>
       </c>
@@ -28285,19 +28303,19 @@
         <v>8</v>
       </c>
       <c r="C426">
-        <v>1040</v>
+        <v>35</v>
       </c>
       <c r="D426" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E426" t="s">
-        <v>53</v>
+        <v>479</v>
       </c>
       <c r="F426" t="s">
-        <v>54</v>
+        <v>480</v>
       </c>
       <c r="G426">
-        <v>6287246</v>
+        <v>6282337</v>
       </c>
       <c r="H426" t="s">
         <v>23</v>
@@ -28309,7 +28327,7 @@
         <v>2</v>
       </c>
       <c r="K426">
-        <v>6287246</v>
+        <v>6282337</v>
       </c>
       <c r="L426" t="s">
         <v>24</v>
@@ -28321,7 +28339,7 @@
         <v>0</v>
       </c>
       <c r="O426">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P426">
         <v>2</v>
@@ -28333,10 +28351,10 @@
         <v>25</v>
       </c>
       <c r="S426">
-        <v>2371960</v>
+        <v>2782610</v>
       </c>
       <c r="T426">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="427" spans="1:20" x14ac:dyDescent="0.35">
@@ -28347,19 +28365,19 @@
         <v>8</v>
       </c>
       <c r="C427">
-        <v>1040</v>
+        <v>36</v>
       </c>
       <c r="D427" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="E427" t="s">
-        <v>53</v>
+        <v>479</v>
       </c>
       <c r="F427" t="s">
-        <v>54</v>
+        <v>480</v>
       </c>
       <c r="G427">
-        <v>6290180</v>
+        <v>6282338</v>
       </c>
       <c r="H427" t="s">
         <v>23</v>
@@ -28371,7 +28389,7 @@
         <v>2</v>
       </c>
       <c r="K427">
-        <v>6290180</v>
+        <v>6282338</v>
       </c>
       <c r="L427" t="s">
         <v>24</v>
@@ -28395,13 +28413,13 @@
         <v>25</v>
       </c>
       <c r="S427">
-        <v>2371960</v>
+        <v>2692386</v>
       </c>
       <c r="T427">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="428" spans="1:20" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="428" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>19</v>
       </c>
@@ -28463,7 +28481,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="429" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>19</v>
       </c>
@@ -28525,7 +28543,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="430" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>19</v>
       </c>
@@ -28587,7 +28605,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="431" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>19</v>
       </c>
@@ -28649,7 +28667,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="432" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>19</v>
       </c>
@@ -28711,7 +28729,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="433" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>19</v>
       </c>
@@ -28773,7 +28791,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="434" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>19</v>
       </c>
@@ -28835,7 +28853,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="435" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>19</v>
       </c>
@@ -28897,7 +28915,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="436" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>19</v>
       </c>
@@ -28959,7 +28977,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="437" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>19</v>
       </c>
@@ -29029,37 +29047,37 @@
         <v>8</v>
       </c>
       <c r="C438">
-        <v>1040</v>
+        <v>37</v>
       </c>
       <c r="D438" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E438" t="s">
-        <v>204</v>
+        <v>479</v>
       </c>
       <c r="F438" t="s">
-        <v>205</v>
+        <v>480</v>
       </c>
       <c r="G438">
-        <v>6291545</v>
+        <v>6269607</v>
       </c>
       <c r="H438" t="s">
         <v>23</v>
       </c>
       <c r="I438">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J438">
         <v>2</v>
       </c>
       <c r="K438">
-        <v>6291545</v>
+        <v>6269607</v>
       </c>
       <c r="L438" t="s">
         <v>24</v>
       </c>
       <c r="M438">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N438">
         <v>0</v>
@@ -29074,13 +29092,13 @@
         <v>0</v>
       </c>
       <c r="R438" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S438">
-        <v>1295362</v>
+        <v>1992818</v>
       </c>
       <c r="T438">
-        <v>2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="439" spans="1:20" x14ac:dyDescent="0.35">
@@ -29091,19 +29109,19 @@
         <v>8</v>
       </c>
       <c r="C439">
-        <v>1040</v>
+        <v>38</v>
       </c>
       <c r="D439" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E439" t="s">
-        <v>204</v>
+        <v>479</v>
       </c>
       <c r="F439" t="s">
-        <v>205</v>
+        <v>480</v>
       </c>
       <c r="G439">
-        <v>6291548</v>
+        <v>6282337</v>
       </c>
       <c r="H439" t="s">
         <v>23</v>
@@ -29115,13 +29133,13 @@
         <v>2</v>
       </c>
       <c r="K439">
-        <v>6291548</v>
+        <v>6282337</v>
       </c>
       <c r="L439" t="s">
         <v>24</v>
       </c>
       <c r="M439">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N439">
         <v>0</v>
@@ -29136,13 +29154,13 @@
         <v>0</v>
       </c>
       <c r="R439" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S439">
-        <v>1295362</v>
+        <v>2782610</v>
       </c>
       <c r="T439">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="440" spans="1:20" x14ac:dyDescent="0.35">
@@ -29153,37 +29171,37 @@
         <v>8</v>
       </c>
       <c r="C440">
-        <v>1040</v>
+        <v>39</v>
       </c>
       <c r="D440" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E440" t="s">
-        <v>204</v>
+        <v>479</v>
       </c>
       <c r="F440" t="s">
-        <v>205</v>
+        <v>480</v>
       </c>
       <c r="G440">
-        <v>6291549</v>
+        <v>6279390</v>
       </c>
       <c r="H440" t="s">
         <v>23</v>
       </c>
       <c r="I440">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J440">
         <v>2</v>
       </c>
       <c r="K440">
-        <v>6291549</v>
+        <v>6279390</v>
       </c>
       <c r="L440" t="s">
         <v>24</v>
       </c>
       <c r="M440">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N440">
         <v>0</v>
@@ -29198,16 +29216,16 @@
         <v>0</v>
       </c>
       <c r="R440" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S440">
-        <v>1295362</v>
+        <v>2615883</v>
       </c>
       <c r="T440">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="441" spans="1:20" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="441" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>19</v>
       </c>
@@ -29269,7 +29287,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="442" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>19</v>
       </c>
@@ -29331,7 +29349,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="443" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>19</v>
       </c>
@@ -29393,7 +29411,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="444" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>19</v>
       </c>
@@ -29455,7 +29473,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="445" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>19</v>
       </c>
@@ -29517,7 +29535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="446" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>19</v>
       </c>
@@ -29579,7 +29597,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="447" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>19</v>
       </c>
@@ -29641,7 +29659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="448" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>19</v>
       </c>
@@ -29703,7 +29721,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="449" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>19</v>
       </c>
@@ -29765,7 +29783,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="450" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>19</v>
       </c>
@@ -29827,7 +29845,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="451" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>19</v>
       </c>
@@ -29889,7 +29907,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="452" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>19</v>
       </c>
@@ -29951,7 +29969,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="453" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>19</v>
       </c>
@@ -30013,7 +30031,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="454" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>19</v>
       </c>
@@ -30083,58 +30101,58 @@
         <v>8</v>
       </c>
       <c r="C455">
-        <v>1040</v>
+        <v>40</v>
       </c>
       <c r="D455" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E455" t="s">
-        <v>369</v>
+        <v>479</v>
       </c>
       <c r="F455" t="s">
-        <v>370</v>
+        <v>480</v>
       </c>
       <c r="G455">
-        <v>6275908</v>
+        <v>6282339</v>
       </c>
       <c r="H455" t="s">
         <v>23</v>
       </c>
       <c r="I455">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J455">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K455">
-        <v>6275908</v>
+        <v>6282339</v>
       </c>
       <c r="L455" t="s">
         <v>24</v>
       </c>
       <c r="M455">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N455">
         <v>0</v>
       </c>
       <c r="O455">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P455">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q455">
         <v>0</v>
       </c>
       <c r="R455" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S455">
-        <v>1683449</v>
+        <v>1032729</v>
       </c>
       <c r="T455">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="456" spans="1:20" x14ac:dyDescent="0.35">
@@ -30145,58 +30163,58 @@
         <v>8</v>
       </c>
       <c r="C456">
-        <v>1040</v>
+        <v>808</v>
       </c>
       <c r="D456" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E456" t="s">
-        <v>369</v>
+        <v>479</v>
       </c>
       <c r="F456" t="s">
-        <v>370</v>
+        <v>480</v>
       </c>
       <c r="G456">
-        <v>6275909</v>
+        <v>6279440</v>
       </c>
       <c r="H456" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I456">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J456">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K456">
-        <v>6275909</v>
+        <v>6279440</v>
       </c>
       <c r="L456" t="s">
         <v>24</v>
       </c>
       <c r="M456">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N456">
         <v>0</v>
       </c>
       <c r="O456">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P456">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q456">
         <v>0</v>
       </c>
       <c r="R456" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S456">
-        <v>1542401</v>
+        <v>1826282</v>
       </c>
       <c r="T456">
-        <v>2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="457" spans="1:20" x14ac:dyDescent="0.35">
@@ -30213,25 +30231,25 @@
         <v>20</v>
       </c>
       <c r="E457" t="s">
-        <v>371</v>
+        <v>479</v>
       </c>
       <c r="F457" t="s">
-        <v>372</v>
+        <v>480</v>
       </c>
       <c r="G457">
-        <v>6275910</v>
+        <v>6270459</v>
       </c>
       <c r="H457" t="s">
         <v>23</v>
       </c>
       <c r="I457">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J457">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K457">
-        <v>6275910</v>
+        <v>6270459</v>
       </c>
       <c r="L457" t="s">
         <v>24</v>
@@ -30243,7 +30261,7 @@
         <v>0</v>
       </c>
       <c r="O457">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P457">
         <v>2</v>
@@ -30252,13 +30270,13 @@
         <v>0</v>
       </c>
       <c r="R457" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S457">
-        <v>2475800</v>
+        <v>2692386</v>
       </c>
       <c r="T457">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458" spans="1:20" x14ac:dyDescent="0.35">
@@ -30275,25 +30293,25 @@
         <v>20</v>
       </c>
       <c r="E458" t="s">
-        <v>371</v>
+        <v>479</v>
       </c>
       <c r="F458" t="s">
-        <v>372</v>
+        <v>480</v>
       </c>
       <c r="G458">
-        <v>6275911</v>
+        <v>6282328</v>
       </c>
       <c r="H458" t="s">
         <v>23</v>
       </c>
       <c r="I458">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J458">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K458">
-        <v>6275911</v>
+        <v>6282328</v>
       </c>
       <c r="L458" t="s">
         <v>24</v>
@@ -30305,7 +30323,7 @@
         <v>0</v>
       </c>
       <c r="O458">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P458">
         <v>2</v>
@@ -30314,13 +30332,13 @@
         <v>0</v>
       </c>
       <c r="R458" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S458">
-        <v>1138064</v>
+        <v>2692386</v>
       </c>
       <c r="T458">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459" spans="1:20" x14ac:dyDescent="0.35">
@@ -30337,13 +30355,13 @@
         <v>20</v>
       </c>
       <c r="E459" t="s">
-        <v>375</v>
+        <v>479</v>
       </c>
       <c r="F459" t="s">
-        <v>376</v>
+        <v>480</v>
       </c>
       <c r="G459">
-        <v>6287671</v>
+        <v>6282338</v>
       </c>
       <c r="H459" t="s">
         <v>23</v>
@@ -30352,40 +30370,40 @@
         <v>1</v>
       </c>
       <c r="J459">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K459">
-        <v>6287671</v>
+        <v>6282338</v>
       </c>
       <c r="L459" t="s">
         <v>24</v>
       </c>
       <c r="M459">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N459">
         <v>0</v>
       </c>
       <c r="O459">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P459">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q459">
         <v>0</v>
       </c>
       <c r="R459" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S459">
-        <v>1609406</v>
+        <v>2692386</v>
       </c>
       <c r="T459">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="460" spans="1:20" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="460" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>19</v>
       </c>
@@ -30447,7 +30465,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="461" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>19</v>
       </c>
@@ -30509,7 +30527,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="462" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>19</v>
       </c>
@@ -30571,7 +30589,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="463" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>19</v>
       </c>
@@ -30633,7 +30651,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="464" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>19</v>
       </c>
@@ -30695,7 +30713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>19</v>
       </c>
@@ -30757,7 +30775,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>19</v>
       </c>
@@ -30819,7 +30837,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>19</v>
       </c>
@@ -30881,7 +30899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>19</v>
       </c>
@@ -30943,7 +30961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>19</v>
       </c>
@@ -31005,7 +31023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>19</v>
       </c>
@@ -31067,7 +31085,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>19</v>
       </c>
@@ -31129,7 +31147,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>19</v>
       </c>
@@ -31191,7 +31209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>19</v>
       </c>
@@ -31253,7 +31271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>19</v>
       </c>
@@ -31315,7 +31333,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>19</v>
       </c>
@@ -31385,31 +31403,31 @@
         <v>8</v>
       </c>
       <c r="C476">
-        <v>1040</v>
+        <v>10355</v>
       </c>
       <c r="D476" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E476" t="s">
-        <v>425</v>
+        <v>479</v>
       </c>
       <c r="F476" t="s">
-        <v>426</v>
+        <v>480</v>
       </c>
       <c r="G476">
-        <v>6275913</v>
+        <v>6279390</v>
       </c>
       <c r="H476" t="s">
         <v>23</v>
       </c>
       <c r="I476">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J476">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K476">
-        <v>6275913</v>
+        <v>6279390</v>
       </c>
       <c r="L476" t="s">
         <v>24</v>
@@ -31421,7 +31439,7 @@
         <v>0</v>
       </c>
       <c r="O476">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P476">
         <v>2</v>
@@ -31430,16 +31448,16 @@
         <v>0</v>
       </c>
       <c r="R476" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S476">
-        <v>2471821</v>
+        <v>2615883</v>
       </c>
       <c r="T476">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="477" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>19</v>
       </c>
@@ -31501,7 +31519,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>19</v>
       </c>
@@ -31563,7 +31581,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>19</v>
       </c>
@@ -31633,37 +31651,37 @@
         <v>8</v>
       </c>
       <c r="C480">
-        <v>1040</v>
+        <v>10526</v>
       </c>
       <c r="D480" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="E480" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="F480" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="G480">
-        <v>6291552</v>
+        <v>6282338</v>
       </c>
       <c r="H480" t="s">
         <v>23</v>
       </c>
       <c r="I480">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J480">
         <v>2</v>
       </c>
       <c r="K480">
-        <v>6291552</v>
+        <v>6282338</v>
       </c>
       <c r="L480" t="s">
         <v>24</v>
       </c>
       <c r="M480">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N480">
         <v>0</v>
@@ -31678,13 +31696,13 @@
         <v>0</v>
       </c>
       <c r="R480" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S480">
-        <v>1833141</v>
+        <v>2692386</v>
       </c>
       <c r="T480">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481" spans="1:20" x14ac:dyDescent="0.35">
@@ -31695,19 +31713,19 @@
         <v>8</v>
       </c>
       <c r="C481">
-        <v>1040</v>
+        <v>10662</v>
       </c>
       <c r="D481" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="E481" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F481" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="G481">
-        <v>6289759</v>
+        <v>6282338</v>
       </c>
       <c r="H481" t="s">
         <v>23</v>
@@ -31719,7 +31737,7 @@
         <v>2</v>
       </c>
       <c r="K481">
-        <v>6289759</v>
+        <v>6282338</v>
       </c>
       <c r="L481" t="s">
         <v>24</v>
@@ -31731,7 +31749,7 @@
         <v>0</v>
       </c>
       <c r="O481">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P481">
         <v>2</v>
@@ -31743,10 +31761,10 @@
         <v>25</v>
       </c>
       <c r="S481">
-        <v>3435711</v>
+        <v>2692386</v>
       </c>
       <c r="T481">
-        <v>65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="482" spans="1:20" x14ac:dyDescent="0.35">
@@ -31757,19 +31775,19 @@
         <v>8</v>
       </c>
       <c r="C482">
-        <v>1040</v>
+        <v>36</v>
       </c>
       <c r="D482" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="E482" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F482" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="G482">
-        <v>6270459</v>
+        <v>6278240</v>
       </c>
       <c r="H482" t="s">
         <v>23</v>
@@ -31778,10 +31796,10 @@
         <v>1</v>
       </c>
       <c r="J482">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K482">
-        <v>6270459</v>
+        <v>6278240</v>
       </c>
       <c r="L482" t="s">
         <v>24</v>
@@ -31793,7 +31811,7 @@
         <v>0</v>
       </c>
       <c r="O482">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P482">
         <v>2</v>
@@ -31802,13 +31820,13 @@
         <v>0</v>
       </c>
       <c r="R482" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S482">
-        <v>2692386</v>
+        <v>2355205</v>
       </c>
       <c r="T482">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="483" spans="1:20" x14ac:dyDescent="0.35">
@@ -31825,13 +31843,13 @@
         <v>20</v>
       </c>
       <c r="E483" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="F483" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="G483">
-        <v>6282328</v>
+        <v>6289759</v>
       </c>
       <c r="H483" t="s">
         <v>23</v>
@@ -31843,7 +31861,7 @@
         <v>2</v>
       </c>
       <c r="K483">
-        <v>6282328</v>
+        <v>6289759</v>
       </c>
       <c r="L483" t="s">
         <v>24</v>
@@ -31855,7 +31873,7 @@
         <v>0</v>
       </c>
       <c r="O483">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P483">
         <v>2</v>
@@ -31867,10 +31885,10 @@
         <v>25</v>
       </c>
       <c r="S483">
-        <v>2692386</v>
+        <v>3435711</v>
       </c>
       <c r="T483">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="484" spans="1:20" x14ac:dyDescent="0.35">
@@ -31881,19 +31899,19 @@
         <v>8</v>
       </c>
       <c r="C484">
-        <v>1040</v>
+        <v>35</v>
       </c>
       <c r="D484" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E484" t="s">
-        <v>479</v>
+        <v>275</v>
       </c>
       <c r="F484" t="s">
-        <v>480</v>
+        <v>276</v>
       </c>
       <c r="G484">
-        <v>6282338</v>
+        <v>6274499</v>
       </c>
       <c r="H484" t="s">
         <v>23</v>
@@ -31902,10 +31920,10 @@
         <v>1</v>
       </c>
       <c r="J484">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K484">
-        <v>6282338</v>
+        <v>6274499</v>
       </c>
       <c r="L484" t="s">
         <v>24</v>
@@ -31929,10 +31947,10 @@
         <v>25</v>
       </c>
       <c r="S484">
-        <v>2692386</v>
+        <v>4339346</v>
       </c>
       <c r="T484">
-        <v>118</v>
+        <v>72</v>
       </c>
     </row>
     <row r="485" spans="1:20" x14ac:dyDescent="0.35">
@@ -31943,19 +31961,19 @@
         <v>8</v>
       </c>
       <c r="C485">
-        <v>10355</v>
+        <v>37</v>
       </c>
       <c r="D485" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E485" t="s">
-        <v>53</v>
+        <v>275</v>
       </c>
       <c r="F485" t="s">
-        <v>54</v>
+        <v>276</v>
       </c>
       <c r="G485">
-        <v>6279383</v>
+        <v>6274499</v>
       </c>
       <c r="H485" t="s">
         <v>23</v>
@@ -31964,10 +31982,10 @@
         <v>1</v>
       </c>
       <c r="J485">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K485">
-        <v>6279383</v>
+        <v>6274499</v>
       </c>
       <c r="L485" t="s">
         <v>24</v>
@@ -31991,13 +32009,13 @@
         <v>25</v>
       </c>
       <c r="S485">
-        <v>2826511</v>
+        <v>4339346</v>
       </c>
       <c r="T485">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="486" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>19</v>
       </c>
@@ -32059,7 +32077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>19</v>
       </c>
@@ -32121,7 +32139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>19</v>
       </c>
@@ -32183,7 +32201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>19</v>
       </c>
@@ -32245,7 +32263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>19</v>
       </c>
@@ -32307,7 +32325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>19</v>
       </c>
@@ -32369,7 +32387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>19</v>
       </c>
@@ -32439,19 +32457,19 @@
         <v>8</v>
       </c>
       <c r="C493">
-        <v>10355</v>
+        <v>38</v>
       </c>
       <c r="D493" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="E493" t="s">
-        <v>479</v>
+        <v>275</v>
       </c>
       <c r="F493" t="s">
-        <v>480</v>
+        <v>276</v>
       </c>
       <c r="G493">
-        <v>6279390</v>
+        <v>6274499</v>
       </c>
       <c r="H493" t="s">
         <v>23</v>
@@ -32460,10 +32478,10 @@
         <v>1</v>
       </c>
       <c r="J493">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K493">
-        <v>6279390</v>
+        <v>6274499</v>
       </c>
       <c r="L493" t="s">
         <v>24</v>
@@ -32487,13 +32505,13 @@
         <v>25</v>
       </c>
       <c r="S493">
-        <v>2615883</v>
+        <v>4339346</v>
       </c>
       <c r="T493">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="494" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>19</v>
       </c>
@@ -32555,7 +32573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>19</v>
       </c>
@@ -32617,7 +32635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>19</v>
       </c>
@@ -32679,7 +32697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>19</v>
       </c>
@@ -32741,7 +32759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>19</v>
       </c>
@@ -32803,7 +32821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>19</v>
       </c>
@@ -32865,7 +32883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="500" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>19</v>
       </c>
@@ -32935,19 +32953,19 @@
         <v>8</v>
       </c>
       <c r="C501">
-        <v>10526</v>
+        <v>40</v>
       </c>
       <c r="D501" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="E501" t="s">
-        <v>479</v>
+        <v>275</v>
       </c>
       <c r="F501" t="s">
-        <v>480</v>
+        <v>276</v>
       </c>
       <c r="G501">
-        <v>6282338</v>
+        <v>6274499</v>
       </c>
       <c r="H501" t="s">
         <v>23</v>
@@ -32956,10 +32974,10 @@
         <v>1</v>
       </c>
       <c r="J501">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K501">
-        <v>6282338</v>
+        <v>6274499</v>
       </c>
       <c r="L501" t="s">
         <v>24</v>
@@ -32983,13 +33001,13 @@
         <v>25</v>
       </c>
       <c r="S501">
-        <v>2692386</v>
+        <v>4339346</v>
       </c>
       <c r="T501">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="502" spans="1:20" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="502" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>19</v>
       </c>
@@ -33051,7 +33069,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="503" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>19</v>
       </c>
@@ -33113,7 +33131,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="504" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>19</v>
       </c>
@@ -33175,7 +33193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>19</v>
       </c>
@@ -33237,7 +33255,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="506" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>19</v>
       </c>
@@ -33299,7 +33317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="507" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>19</v>
       </c>
@@ -33361,7 +33379,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="508" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>19</v>
       </c>
@@ -33423,7 +33441,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="509" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>19</v>
       </c>
@@ -33493,19 +33511,19 @@
         <v>8</v>
       </c>
       <c r="C510">
-        <v>10662</v>
+        <v>37</v>
       </c>
       <c r="D510" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="E510" t="s">
-        <v>479</v>
+        <v>42</v>
       </c>
       <c r="F510" t="s">
-        <v>480</v>
+        <v>43</v>
       </c>
       <c r="G510">
-        <v>6282338</v>
+        <v>6269609</v>
       </c>
       <c r="H510" t="s">
         <v>23</v>
@@ -33514,10 +33532,10 @@
         <v>1</v>
       </c>
       <c r="J510">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K510">
-        <v>6282338</v>
+        <v>6269609</v>
       </c>
       <c r="L510" t="s">
         <v>24</v>
@@ -33538,10 +33556,10 @@
         <v>0</v>
       </c>
       <c r="R510" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S510">
-        <v>2692386</v>
+        <v>5746361</v>
       </c>
       <c r="T510">
         <v>7</v>
